--- a/data/output/bro_summary.xlsx
+++ b/data/output/bro_summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t>bro</t>
   </si>
@@ -37,19 +37,40 @@
     <t>ledgerValue</t>
   </si>
   <si>
+    <t>assignedLimit</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
     <t xml:space="preserve">N/A </t>
   </si>
   <si>
+    <t>KUBER THAPA</t>
+  </si>
+  <si>
     <t>LAXMAN LIMBU SUBBA</t>
   </si>
   <si>
-    <t>TANK PRASAD GAUTAM</t>
+    <t>RAM CHANDRA POKHAREL</t>
+  </si>
+  <si>
+    <t>TIKA BAHADUR GOTAME</t>
+  </si>
+  <si>
+    <t>233742</t>
   </si>
   <si>
     <t>236901</t>
   </si>
   <si>
-    <t>11</t>
+    <t>216199</t>
+  </si>
+  <si>
+    <t>1744740</t>
+  </si>
+  <si>
+    <t>CRED</t>
   </si>
 </sst>
 </file>
@@ -407,10 +428,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -432,51 +453,127 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D2">
-        <v>14890378.1</v>
+        <v>48401880</v>
       </c>
       <c r="E2">
-        <v>-514422.25</v>
+        <v>-5521353.11</v>
       </c>
       <c r="F2">
-        <v>-32.03</v>
+        <v>-137.03</v>
       </c>
       <c r="G2">
-        <v>517639.77</v>
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3">
+        <v>15898286.3</v>
+      </c>
+      <c r="E3">
+        <v>9155.75</v>
+      </c>
+      <c r="F3">
+        <v>2.619999999999999</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>17480718.7</v>
-      </c>
-      <c r="E3">
-        <v>-1583190.08</v>
-      </c>
-      <c r="F3">
-        <v>2758.46</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4">
+        <v>2973679</v>
+      </c>
+      <c r="E4">
+        <v>-806210.7200000001</v>
+      </c>
+      <c r="F4">
+        <v>-45.06999999999999</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <v>156142.6</v>
+      </c>
+      <c r="E5">
+        <v>-10173.32</v>
+      </c>
+      <c r="F5">
+        <v>1773.06</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/bro_summary.xlsx
+++ b/data/output/bro_summary.xlsx
@@ -471,13 +471,13 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>48401880</v>
+        <v>48556729.3</v>
       </c>
       <c r="E2">
-        <v>-5521353.11</v>
+        <v>-5355414.470000001</v>
       </c>
       <c r="F2">
-        <v>-137.03</v>
+        <v>-135.5</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -500,13 +500,13 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>15898286.3</v>
+        <v>15707667.8</v>
       </c>
       <c r="E3">
-        <v>9155.75</v>
+        <v>37565.13999999998</v>
       </c>
       <c r="F3">
-        <v>2.619999999999999</v>
+        <v>-0.5499999999999989</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -529,13 +529,13 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>2973679</v>
+        <v>2958990</v>
       </c>
       <c r="E4">
-        <v>-806210.7200000001</v>
+        <v>-821951.65</v>
       </c>
       <c r="F4">
-        <v>-45.06999999999999</v>
+        <v>-45.95</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -558,13 +558,13 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>156142.6</v>
+        <v>156651</v>
       </c>
       <c r="E5">
-        <v>-10173.32</v>
+        <v>-9628.520000000004</v>
       </c>
       <c r="F5">
-        <v>1773.06</v>
+        <v>1775.6</v>
       </c>
       <c r="G5">
         <v>0</v>
